--- a/Master Quotation Details 2026_V0.xlsx
+++ b/Master Quotation Details 2026_V0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\Downloads\JAWS QUOTE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BD02E6-9866-43C9-B7AB-0437FAB1A6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A39B57-3375-4813-8925-DD48D79DB355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
